--- a/wwwroot/assets/template/Story_Template.xlsx
+++ b/wwwroot/assets/template/Story_Template.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ASP.NET\WebTruyenTranh\wwwroot\assets\template\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\HP\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{512C6F0D-7C50-4F82-B81E-05EFC425651B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57FD38B1-9C55-484E-89DF-99803630A23E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,14 +20,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="22">
   <si>
     <t>LIST OF STORIES</t>
   </si>
   <si>
-    <t>Export date: 27/01/2026 20:28:31</t>
-  </si>
-  <si>
     <t>Total stories: 1</t>
   </si>
   <si>
@@ -49,18 +46,9 @@
     <t>CategoryIds</t>
   </si>
   <si>
-    <t>Nguyễn Văn Huy</t>
-  </si>
-  <si>
     <t>Completed</t>
   </si>
   <si>
-    <t>Hoạt hình,Lịch sử,Tình cảm</t>
-  </si>
-  <si>
-    <t>ghi mô tả</t>
-  </si>
-  <si>
     <t>AuthorName</t>
   </si>
   <si>
@@ -73,13 +61,31 @@
     <t>Tiếng Anh, tiếng Việt, tiếng Trung, tiếng Nhật, tiếng Pháp</t>
   </si>
   <si>
-    <t>Truyện mẫu 1</t>
-  </si>
-  <si>
-    <t>Truyện mẫu 2</t>
-  </si>
-  <si>
-    <t>Hoạt hình,Tình cảm</t>
+    <t>Test 1</t>
+  </si>
+  <si>
+    <t>Test 2</t>
+  </si>
+  <si>
+    <t>hello1</t>
+  </si>
+  <si>
+    <t>hello2</t>
+  </si>
+  <si>
+    <t>Lev Tolstoy</t>
+  </si>
+  <si>
+    <t>Fyodor Dostoevsky</t>
+  </si>
+  <si>
+    <t>Drama, Comedy</t>
+  </si>
+  <si>
+    <t>Horror, Fantasy</t>
+  </si>
+  <si>
+    <t>Export date: 27/09/2026 20:28:31</t>
   </si>
 </sst>
 </file>
@@ -138,6 +144,7 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -147,7 +154,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -446,16 +452,16 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:13" ht="23.4" x14ac:dyDescent="0.45">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
+      <c r="B1" s="4"/>
+      <c r="C1" s="5"/>
+      <c r="D1" s="5"/>
+      <c r="E1" s="5"/>
+      <c r="F1" s="5"/>
+      <c r="G1" s="5"/>
+      <c r="H1" s="5"/>
       <c r="I1" s="2"/>
       <c r="J1" s="2"/>
       <c r="K1" s="2"/>
@@ -463,105 +469,105 @@
       <c r="M1" s="2"/>
     </row>
     <row r="2" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A2" s="5" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="6"/>
-      <c r="D2" s="6"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
+      <c r="A2" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="B2" s="6"/>
+      <c r="C2" s="7"/>
+      <c r="D2" s="7"/>
+      <c r="E2" s="7"/>
+      <c r="F2" s="7"/>
+      <c r="G2" s="7"/>
+      <c r="H2" s="7"/>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
-      <c r="A3" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="7"/>
-      <c r="C3" s="6"/>
-      <c r="D3" s="6"/>
-      <c r="E3" s="6"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6"/>
+      <c r="A3" s="8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" s="8"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="7"/>
+      <c r="F3" s="7"/>
+      <c r="G3" s="7"/>
+      <c r="H3" s="7"/>
     </row>
     <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A5" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B5" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="1" t="s">
+      <c r="C5" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="1" t="s">
+      <c r="D5" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="E5" s="2" t="s">
-        <v>14</v>
-      </c>
-      <c r="F5" s="1" t="s">
+      <c r="G5" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="G5" s="1" t="s">
+      <c r="H5" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="H5" s="1" t="s">
-        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="C6">
         <v>33</v>
       </c>
       <c r="D6" t="s">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="E6" t="s">
-        <v>15</v>
-      </c>
-      <c r="F6" s="8">
+        <v>11</v>
+      </c>
+      <c r="F6" s="3">
         <v>39617</v>
       </c>
       <c r="G6" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H6" t="s">
-        <v>11</v>
+        <v>19</v>
       </c>
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7">
+        <v>21</v>
+      </c>
+      <c r="D7" t="s">
         <v>18</v>
       </c>
-      <c r="B7" t="s">
+      <c r="E7" t="s">
         <v>12</v>
       </c>
-      <c r="C7">
-        <v>33</v>
-      </c>
-      <c r="D7" t="s">
-        <v>9</v>
-      </c>
-      <c r="E7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F7" s="8">
+      <c r="F7" s="3">
         <v>39617</v>
       </c>
       <c r="G7" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="H7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
